--- a/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v5/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v5/Contrary(P)Body(N).xlsx
@@ -30681,16 +30681,16 @@
         <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9232673267326733</v>
+        <v>0.9232669999999999</v>
       </c>
       <c r="M2" t="n">
         <v>0.9325</v>
       </c>
       <c r="N2" t="n">
-        <v>0.927860696517413</v>
+        <v>0.927861</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8725274725274725</v>
+        <v>0.8725270000000001</v>
       </c>
     </row>
     <row r="3">
@@ -30740,16 +30740,16 @@
         <v>28</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.923077</v>
       </c>
       <c r="M3" t="n">
         <v>0.93</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9265255292652554</v>
+        <v>0.926526</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8703296703296703</v>
+        <v>0.87033</v>
       </c>
     </row>
     <row r="4">
@@ -30799,16 +30799,16 @@
         <v>28</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.923077</v>
       </c>
       <c r="M4" t="n">
         <v>0.93</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9265255292652554</v>
+        <v>0.926526</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8703296703296703</v>
+        <v>0.87033</v>
       </c>
     </row>
   </sheetData>
